--- a/artfynd/A 44274-2025 artfynd.xlsx
+++ b/artfynd/A 44274-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734713</v>
       </c>
       <c r="B2" t="n">
-        <v>79017</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131732980</v>
       </c>
       <c r="B3" t="n">
-        <v>80400</v>
+        <v>80401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738106</v>
       </c>
       <c r="B4" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44274-2025 artfynd.xlsx
+++ b/artfynd/A 44274-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734713</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131732980</v>
       </c>
       <c r="B3" t="n">
-        <v>80401</v>
+        <v>80404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738106</v>
       </c>
       <c r="B4" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44274-2025 artfynd.xlsx
+++ b/artfynd/A 44274-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734713</v>
       </c>
       <c r="B2" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131732980</v>
       </c>
       <c r="B3" t="n">
-        <v>80404</v>
+        <v>80406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738106</v>
       </c>
       <c r="B4" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44274-2025 artfynd.xlsx
+++ b/artfynd/A 44274-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734713</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131732980</v>
       </c>
       <c r="B3" t="n">
-        <v>80406</v>
+        <v>80409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738106</v>
       </c>
       <c r="B4" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44274-2025 artfynd.xlsx
+++ b/artfynd/A 44274-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734713</v>
       </c>
       <c r="B2" t="n">
-        <v>79026</v>
+        <v>79031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131732980</v>
       </c>
       <c r="B3" t="n">
-        <v>80409</v>
+        <v>80414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738106</v>
       </c>
       <c r="B4" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44274-2025 artfynd.xlsx
+++ b/artfynd/A 44274-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734713</v>
       </c>
       <c r="B2" t="n">
-        <v>79031</v>
+        <v>79033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131732980</v>
       </c>
       <c r="B3" t="n">
-        <v>80414</v>
+        <v>80416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738106</v>
       </c>
       <c r="B4" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44274-2025 artfynd.xlsx
+++ b/artfynd/A 44274-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734713</v>
       </c>
       <c r="B2" t="n">
-        <v>79033</v>
+        <v>79067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131732980</v>
       </c>
       <c r="B3" t="n">
-        <v>80416</v>
+        <v>80450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738106</v>
       </c>
       <c r="B4" t="n">
-        <v>80381</v>
+        <v>80415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44274-2025 artfynd.xlsx
+++ b/artfynd/A 44274-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734713</v>
       </c>
       <c r="B2" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131732980</v>
       </c>
       <c r="B3" t="n">
-        <v>80455</v>
+        <v>80457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738106</v>
       </c>
       <c r="B4" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
